--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:45</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G12" s="2"/>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" s="2"/>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G29" s="2"/>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G30" s="2"/>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:35</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
